--- a/data/firms/the5ers.xlsx
+++ b/data/firms/the5ers.xlsx
@@ -2610,7 +2610,11 @@
           <t>evaluation</t>
         </is>
       </c>
-      <c r="H5" s="16" t="n"/>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
           <t>oui</t>
@@ -3138,7 +3142,11 @@
       </c>
       <c r="F18" s="16" t="n"/>
       <c r="G18" s="16" t="n"/>
-      <c r="H18" s="16" t="n"/>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
           <t>oui</t>
@@ -3276,11 +3284,7 @@
       </c>
       <c r="F21" s="16" t="n"/>
       <c r="G21" s="16" t="n"/>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="H21" s="16" t="n"/>
       <c r="I21" s="16" t="inlineStr">
         <is>
           <t>oui</t>
@@ -3400,11 +3404,7 @@
       </c>
       <c r="F24" s="16" t="n"/>
       <c r="G24" s="16" t="n"/>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="H24" s="16" t="n"/>
       <c r="I24" s="16" t="inlineStr">
         <is>
           <t>oui</t>
@@ -3444,11 +3444,7 @@
       </c>
       <c r="F25" s="16" t="n"/>
       <c r="G25" s="16" t="n"/>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="H25" s="16" t="n"/>
       <c r="I25" s="16" t="inlineStr">
         <is>
           <t>oui</t>
@@ -3484,11 +3480,7 @@
       <c r="E26" s="16" t="n"/>
       <c r="F26" s="16" t="n"/>
       <c r="G26" s="16" t="n"/>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="H26" s="16" t="n"/>
       <c r="I26" s="16" t="inlineStr">
         <is>
           <t>oui</t>
@@ -3764,11 +3756,7 @@
       </c>
       <c r="F33" s="16" t="n"/>
       <c r="G33" s="16" t="n"/>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="H33" s="16" t="n"/>
       <c r="I33" s="16" t="n"/>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -3804,11 +3792,7 @@
       </c>
       <c r="F34" s="16" t="n"/>
       <c r="G34" s="16" t="n"/>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="H34" s="16" t="n"/>
       <c r="I34" s="16" t="n"/>
       <c r="J34" s="16" t="inlineStr">
         <is>

--- a/data/firms/the5ers.xlsx
+++ b/data/firms/the5ers.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1488,6 +1488,18 @@
       <c r="D9" s="18" t="inlineStr">
         <is>
           <t>Seule une offre confirmed s'affiche : remise, code, Copy code et Claim deal. Vide ou needs_confirmation : la carte garde le plan, le prix public et Continue to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>accroche</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Une phrase courte pour le bandeau de campagne du site : ce que l'offre donne, en plus du pourcentage. Vide : le bandeau n'affiche que la remise.</t>
         </is>
       </c>
     </row>

--- a/data/firms/the5ers.xlsx
+++ b/data/firms/the5ers.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1500,6 +1500,30 @@
       <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Une phrase courte pour le bandeau de campagne du site : ce que l'offre donne, en plus du pourcentage. Vide : le bandeau n'affiche que la remise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>remise_campagne</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Taux d'une campagne a duree limitee, en %. Il remplace « remise » jusqu'a « campagne_fin », puis la fiche revient a « remise ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>campagne_fin</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Fin de la campagne, date et heure ISO. Passee, le taux de campagne et l'accroche disparaissent, l'offre permanente reste.</t>
         </is>
       </c>
     </row>

--- a/data/firms/the5ers.xlsx
+++ b/data/firms/the5ers.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1524,6 +1524,18 @@
       <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Fin de la campagne, date et heure ISO. Passee, le taux de campagne et l'accroche disparaissent, l'offre permanente reste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>bonus</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Deux ou trois mots pour ce que l'offre donne en plus du pourcentage (« +1 free reset »). Affiche en pastille sur la fiche et sur la carte /compare. Suit la campagne : il disparait avec elle.</t>
         </is>
       </c>
     </row>

--- a/data/firms/the5ers.xlsx
+++ b/data/firms/the5ers.xlsx
@@ -17,15 +17,16 @@
     <sheet name="Phases" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="OptionsAchat" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Offre" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Conditions" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Parcours" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Formation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ComptesApresReussite" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Couts" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Regles" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Verdict" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="FAQ" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Listes" sheetId="19" state="hidden" r:id="rId19"/>
+    <sheet name="Campagnes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Conditions" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Parcours" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Formation" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ComptesApresReussite" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Couts" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Regles" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Verdict" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="FAQ" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Listes" sheetId="20" state="hidden" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1559,6 +1560,92 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>debut</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>remise</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Date et heure ISO d'ouverture. Avant elle, la campagne n'existe nulle part.</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>Date et heure ISO de fermeture. Passee, la campagne disparait d'elle-meme.</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="inlineStr">
+        <is>
+          <t>Deux ou trois mots, pour la pastille : « Day 4 · -60% TCP25 ».</t>
+        </is>
+      </c>
+      <c r="D2" s="25" t="inlineStr">
+        <is>
+          <t>Une phrase : ce que l'offre donne, telle qu'elle s'affiche.</t>
+        </is>
+      </c>
+      <c r="E2" s="25" t="inlineStr">
+        <is>
+          <t>Taux pendant la fenetre, en %. Vide : le taux habituel de l'offre ne change pas.</t>
+        </is>
+      </c>
+      <c r="F2" s="25" t="inlineStr">
+        <is>
+          <t>confirmed pour s'afficher. Toute autre valeur la garde en reserve.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="004B5563"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1654,7 +1741,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -1857,7 +1944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -1967,7 +2054,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -2156,7 +2243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -2402,7 +2489,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -4743,7 +4830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006B7280"/>
@@ -5048,7 +5135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006B7280"/>
@@ -5233,7 +5320,581 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F2937"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Champ</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Valeur a remplir</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Exemple — FuturesElite, 7 sept. 2026</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Ou ca s'affiche dans le HTML · si vide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>slug</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>the5ers</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>futureselite</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>N'est pas affiche : sert a l'adresse de la page et au lien sortant. Minuscules, sans espace. Obligatoire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>The5ers</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>FuturesElite</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>Le titre de la carte d'identite, « Continue to [Firm] », le verdict et la FAQ. Obligatoire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>logo_url</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>https://the5ers.com/wp-content/uploads/2023/01/favicon.png</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>https://www.google.com/s2/favicons?domain=futureselite.com&amp;sz=128</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Le logo, en tuile blanche. Il n'est pas cliquable : les sorties passent par Claim deal et Continue to. Vide : initiale du nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_score</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Hero, angle haut droit : note sur 5. Vide : le bloc Trustpilot n'apparait pas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_review_count</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n">
+        <v>38563</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Nombre d'avis sous la note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_url</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>https://www.trustpilot.com/review/the5ers.com</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>https://www.trustpilot.com/review/exemple.com</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Page Trustpilot de la firme : le badge y renvoie. Vide : badge non cliquable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>marches</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>cfd, futures</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>futures</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Ten years of funded trading, with no time limit</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Four routes to a funded futures account</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : le H1, une proposition de valeur. Vide : le nom de la firme sert de H1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Founded in 2016, The5ers is one of the oldest CFD prop firms still trading. No evaluation has a deadline, every CFD drawdown is static rather than trailing, and positions can be held overnight and over the weekend. Four routes, from $2,500 to instant funding, plus a futures line launched in 2026.</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase.</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : 2 a 3 lignes sous le H1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>resume</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement (retour arriere) : 1 a 2 phrases sous le nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>presentation</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>The5ers was founded in 2016 and trades as FIVE PERCENT ONLINE LTD, registered in Israel and in the United Kingdom. It is not regulated and does not provide financial services: it funds traders on its own capital, through commercial liquidity providers it does not name.
+The firm says it employs 171 people across 24 countries, has onboarded 262,000 traders and opened more than 1.6 million trading accounts.
+Four routes sit side by side. Pro Growth is a single evaluation phase. High Stakes is the two-step route, with the fee refunded in stages. Hyper Growth funds you from purchase and doubles the account at every 10% target. The futures line, launched separately, trades CME contracts on BlackArrow.</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>annee_creation</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>« Founded ». Vide : « — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>pays</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>« Country ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>ceo_fondateur</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Gil Ben Hur</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Christian Habibi</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>« CEO / Founder ». Vide : « — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>actifs</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement : une etiquette par actif, separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>categories_actifs</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Forex, Indices, Metals, Commodities, Crypto, Futures</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>(vide — non confirmees)</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page, « Tradable assets » : categories precises (Index futures, Currency futures…), seulement si confirmees par la firme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>categories_actifs_statut</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>needs_confirmation</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>confirmed si la liste est confirmee. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>plateformes</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement. La nouvelle lit l'onglet Plateformes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>moyens_paiement</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Credit/Debit Card, Crypto</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>« Purchase methods » : moyens de paiement A L'ACHAT, separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>methodes_retrait</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Rise, Crypto, Bank transfer, Hub Credits</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Crypto, Riseworks</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>Carte PAYOUTS : methodes de RETRAIT, separees par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>prestataire_retrait</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Rise</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Rise</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>Carte PAYOUTS : le prestataire qui paie les retraits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>levier</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>N/A (futures contracts)</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>levier_statut</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : confirmed si levier est rempli. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>styles_trading</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Day trading, Swing</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>(vide — absent du releve)</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>meta_description</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>flux_donnees</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Carte « Data feeds » : flux de donnees proposes, separes par des virgules. Affichage seulement.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$A$2:$A$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$A$2:$A$6</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009CA3AF"/>
@@ -5611,580 +6272,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001F2937"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Champ</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Valeur a remplir</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Exemple — FuturesElite, 7 sept. 2026</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Ou ca s'affiche dans le HTML · si vide</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>slug</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>the5ers</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>futureselite</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>N'est pas affiche : sert a l'adresse de la page et au lien sortant. Minuscules, sans espace. Obligatoire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>nom</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>The5ers</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>FuturesElite</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>Le titre de la carte d'identite, « Continue to [Firm] », le verdict et la FAQ. Obligatoire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>logo_url</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>https://the5ers.com/wp-content/uploads/2023/01/favicon.png</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>https://www.google.com/s2/favicons?domain=futureselite.com&amp;sz=128</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>Le logo, en tuile blanche. Il n'est pas cliquable : les sorties passent par Claim deal et Continue to. Vide : initiale du nom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_score</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="C5" s="20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>Hero, angle haut droit : note sur 5. Vide : le bloc Trustpilot n'apparait pas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_review_count</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n">
-        <v>38563</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>Nombre d'avis sous la note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_url</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>https://www.trustpilot.com/review/the5ers.com</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>https://www.trustpilot.com/review/exemple.com</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>Page Trustpilot de la firme : le badge y renvoie. Vide : badge non cliquable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>marches</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>cfd, futures</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>futures</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>titre</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Ten years of funded trading, with no time limit</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Four routes to a funded futures account</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : le H1, une proposition de valeur. Vide : le nom de la firme sert de H1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Founded in 2016, The5ers is one of the oldest CFD prop firms still trading. No evaluation has a deadline, every CFD drawdown is static rather than trailing, and positions can be held overnight and over the weekend. Four routes, from $2,500 to instant funding, plus a futures line launched in 2026.</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase.</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : 2 a 3 lignes sous le H1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>resume</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement (retour arriere) : 1 a 2 phrases sous le nom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>presentation</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>The5ers was founded in 2016 and trades as FIVE PERCENT ONLINE LTD, registered in Israel and in the United Kingdom. It is not regulated and does not provide financial services: it funds traders on its own capital, through commercial liquidity providers it does not name.
-The firm says it employs 171 people across 24 countries, has onboarded 262,000 traders and opened more than 1.6 million trading accounts.
-Four routes sit side by side. Pro Growth is a single evaluation phase. High Stakes is the two-step route, with the fee refunded in stages. Hyper Growth funds you from purchase and doubles the account at every 10% target. The futures line, launched separately, trades CME contracts on BlackArrow.</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>annee_creation</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C13" s="24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>« Founded ». Vide : « — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>pays</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Israel</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>« Country ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>ceo_fondateur</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>Gil Ben Hur</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>Christian Habibi</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>« CEO / Founder ». Vide : « — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>actifs</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement : une etiquette par actif, separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>categories_actifs</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>Forex, Indices, Metals, Commodities, Crypto, Futures</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>(vide — non confirmees)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page, « Tradable assets » : categories precises (Index futures, Currency futures…), seulement si confirmees par la firme.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>categories_actifs_statut</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>needs_confirmation</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>confirmed si la liste est confirmee. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>plateformes</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement. La nouvelle lit l'onglet Plateformes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>moyens_paiement</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Credit/Debit Card, Crypto</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>« Purchase methods » : moyens de paiement A L'ACHAT, separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>methodes_retrait</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Rise, Crypto, Bank transfer, Hub Credits</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Crypto, Riseworks</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>Carte PAYOUTS : methodes de RETRAIT, separees par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>prestataire_retrait</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>Rise</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>Rise</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>Carte PAYOUTS : le prestataire qui paie les retraits.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>levier</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>N/A (futures contracts)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>levier_statut</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : confirmed si levier est rempli. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>styles_trading</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>Day trading, Swing</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>(vide — absent du releve)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>meta_description</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>flux_donnees</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>Carte « Data feeds » : flux de donnees proposes, separes par des virgules. Affichage seulement.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$A$2:$A$6</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
